--- a/data/dividends_info_20260530.xlsx
+++ b/data/dividends_info_20260530.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K168"/>
+  <dimension ref="A1:K158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5661,11 +5661,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.17</v>
+        <v>0.297</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5689,14 +5689,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IT0005453748</t>
+          <t>IT0005568461</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3.299999952316284</v>
+        <v>7.099999904632568</v>
       </c>
       <c r="I112" t="n">
-        <v>5.151515225952543</v>
+        <v>4.183098647736813</v>
       </c>
       <c r="J112" t="n">
         <v>-12</v>
@@ -5708,11 +5708,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>IT0005373789</t>
+          <t>IT0001206769</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>23.25</v>
+        <v>56.5</v>
       </c>
       <c r="I113" t="n">
-        <v>3.010752688172043</v>
+        <v>0.7964601769911505</v>
       </c>
       <c r="J113" t="n">
         <v>-12</v>
@@ -5755,11 +5755,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5783,14 +5783,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IT0005378143</t>
+          <t>IT0005595423</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2.420000076293945</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I114" t="n">
-        <v>1.446280946139471</v>
+        <v>0.7017544094471985</v>
       </c>
       <c r="J114" t="n">
         <v>-12</v>
@@ -5802,11 +5802,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.33</v>
+        <v>1.05</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IT0005054967</t>
+          <t>IT0003549422</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.650000095367432</v>
+        <v>37.04000091552734</v>
       </c>
       <c r="I115" t="n">
-        <v>5.840707866015344</v>
+        <v>2.834773148074722</v>
       </c>
       <c r="J115" t="n">
         <v>-12</v>
@@ -5849,11 +5849,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5877,14 +5877,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>IT0004931496</t>
+          <t>IT0005621070</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.9210000038146973</v>
+        <v>1.5</v>
       </c>
       <c r="I116" t="n">
-        <v>7.600434279051732</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J116" t="n">
         <v>-12</v>
@@ -5896,11 +5896,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.71</v>
+        <v>0.38</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>IT0003828271</t>
+          <t>IT0005162406</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>51.5</v>
+        <v>17.80999946594238</v>
       </c>
       <c r="I117" t="n">
-        <v>1.378640776699029</v>
+        <v>2.133632854547046</v>
       </c>
       <c r="J117" t="n">
         <v>-12</v>
@@ -5943,15 +5943,15 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5971,14 +5971,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>IT0005282865</t>
+          <t>LU2598331598</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>102.9000015258789</v>
+        <v>26.09000015258789</v>
       </c>
       <c r="I118" t="n">
-        <v>1.311953333315045</v>
+        <v>2.299731684518543</v>
       </c>
       <c r="J118" t="n">
         <v>-12</v>
@@ -5990,11 +5990,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.08</v>
+        <v>0.35</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6018,14 +6018,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>IT0005543613</t>
+          <t>IT0001454435</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>7.239999771118164</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="I119" t="n">
-        <v>1.104972410622668</v>
+        <v>0.9615384212310112</v>
       </c>
       <c r="J119" t="n">
         <v>-12</v>
@@ -6037,11 +6037,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3</v>
+        <v>0.017</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6065,14 +6065,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>IT0001017851</t>
+          <t>IT0005658841</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>264</v>
+        <v>3.160000085830688</v>
       </c>
       <c r="I120" t="n">
-        <v>1.136363636363636</v>
+        <v>0.5379746689320455</v>
       </c>
       <c r="J120" t="n">
         <v>-12</v>
@@ -6084,11 +6084,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.17</v>
+        <v>0.01</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6112,14 +6112,14 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>IT0005495657</t>
+          <t>IT0005573065</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.119999885559082</v>
+        <v>2.845000028610229</v>
       </c>
       <c r="I121" t="n">
-        <v>4.126213706846526</v>
+        <v>0.3514938453229105</v>
       </c>
       <c r="J121" t="n">
         <v>-12</v>
@@ -6131,11 +6131,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.297</v>
+        <v>1.12</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6159,14 +6159,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>IT0005568461</t>
+          <t>IT0004810054</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>7.099999904632568</v>
+        <v>21.23999977111816</v>
       </c>
       <c r="I122" t="n">
-        <v>4.183098647736813</v>
+        <v>5.27306973667184</v>
       </c>
       <c r="J122" t="n">
         <v>-12</v>
@@ -6178,11 +6178,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6206,14 +6206,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>IT0001206769</t>
+          <t>IT0004717200</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>56.5</v>
+        <v>1.389999985694885</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7964601769911505</v>
+        <v>7.194244678355753</v>
       </c>
       <c r="J123" t="n">
         <v>-12</v>
@@ -6225,11 +6225,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6253,14 +6253,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>IT0005595423</t>
+          <t>IT0003865588</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5.699999809265137</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7017544094471985</v>
+        <v>2.813852883554092</v>
       </c>
       <c r="J124" t="n">
         <v>-12</v>
@@ -6272,11 +6272,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1.05</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6300,14 +6300,14 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>IT0003549422</t>
+          <t>IT0005610958</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>37.04000091552734</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I125" t="n">
-        <v>2.834773148074722</v>
+        <v>4.120535696742638</v>
       </c>
       <c r="J125" t="n">
         <v>-12</v>
@@ -6319,11 +6319,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6332,12 +6332,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6347,30 +6347,30 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>IT0005621070</t>
+          <t>IT0001006128</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1.5</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I126" t="n">
-        <v>3.333333333333333</v>
+        <v>3.804347904958889</v>
       </c>
       <c r="J126" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="K126" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.38</v>
+        <v>0.096</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -6379,12 +6379,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6394,44 +6394,44 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>IT0005162406</t>
+          <t>IT0005543332</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>17.80999946594238</v>
+        <v>5.199999809265137</v>
       </c>
       <c r="I127" t="n">
-        <v>2.133632854547046</v>
+        <v>1.846153913870368</v>
       </c>
       <c r="J127" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="K127" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6441,30 +6441,30 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>LU2598331598</t>
+          <t>IT0005416281</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>26.09000015258789</v>
+        <v>6.25</v>
       </c>
       <c r="I128" t="n">
-        <v>2.299731684518543</v>
+        <v>4.8</v>
       </c>
       <c r="J128" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="K128" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6473,12 +6473,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6488,30 +6488,30 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>IT0001454435</t>
+          <t>IT0005037905</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>36.40000152587891</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9615384212310112</v>
+        <v>1.754386023617996</v>
       </c>
       <c r="J129" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="K129" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.017</v>
+        <v>0.06</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -6520,45 +6520,45 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>IT0005658841</t>
+          <t>IT0005337818</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>3.160000085830688</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5379746689320455</v>
+        <v>0.6521739265643809</v>
       </c>
       <c r="J130" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="K130" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -6567,12 +6567,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6582,30 +6582,30 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>IT0005573065</t>
+          <t>IT0005075764</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2.845000028610229</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3514938453229105</v>
+        <v>2.64550269889837</v>
       </c>
       <c r="J131" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="K131" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1.12</v>
+        <v>0.06</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6629,30 +6629,30 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>IT0004810054</t>
+          <t>IT0004376858</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>21.23999977111816</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I132" t="n">
-        <v>5.27306973667184</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J132" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="K132" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6661,12 +6661,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6676,30 +6676,30 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>IT0004717200</t>
+          <t>IT0005138703</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1.389999985694885</v>
+        <v>15.53999996185303</v>
       </c>
       <c r="I133" t="n">
-        <v>7.194244678355753</v>
+        <v>3.217503225401416</v>
       </c>
       <c r="J133" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="K133" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6708,12 +6708,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6723,30 +6723,30 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>IT0003865588</t>
+          <t>IT0005430951</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.239999771118164</v>
+        <v>3.660000085830688</v>
       </c>
       <c r="I134" t="n">
-        <v>2.813852883554092</v>
+        <v>2.73224037308468</v>
       </c>
       <c r="J134" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="K134" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6770,30 +6770,30 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>IT0005610958</t>
+          <t>IT0005339160</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.240000009536743</v>
+        <v>3.170000076293945</v>
       </c>
       <c r="I135" t="n">
-        <v>4.120535696742638</v>
+        <v>3.470031462226375</v>
       </c>
       <c r="J135" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="K135" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.35</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6817,14 +6817,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>IT0001006128</t>
+          <t>IT0005545238</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>9.199999809265137</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I136" t="n">
-        <v>3.804347904958889</v>
+        <v>0.9550562207106782</v>
       </c>
       <c r="J136" t="n">
         <v>-19</v>
@@ -6836,11 +6836,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>IT0005543332</t>
+          <t>IT0005466963</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>5.199999809265137</v>
+        <v>4.820000171661377</v>
       </c>
       <c r="I137" t="n">
-        <v>1.846153913870368</v>
+        <v>1.970954286652131</v>
       </c>
       <c r="J137" t="n">
         <v>-19</v>
@@ -6883,11 +6883,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -6911,14 +6911,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>IT0005416281</t>
+          <t>IT0005521551</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>6.25</v>
+        <v>1.25</v>
       </c>
       <c r="I138" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J138" t="n">
         <v>-19</v>
@@ -6930,11 +6930,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6958,14 +6958,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>IT0005037905</t>
+          <t>IT0005246142</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>11.39999961853027</v>
+        <v>7.949999809265137</v>
       </c>
       <c r="I139" t="n">
-        <v>1.754386023617996</v>
+        <v>1.13207549885865</v>
       </c>
       <c r="J139" t="n">
         <v>-19</v>
@@ -6977,11 +6977,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7000,19 +7000,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>IT0005337818</t>
+          <t>IT0005532525</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>9.199999809265137</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6521739265643809</v>
+        <v>1.190476244539363</v>
       </c>
       <c r="J140" t="n">
         <v>-19</v>
@@ -7024,11 +7024,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7052,14 +7052,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>IT0005075764</t>
+          <t>IT0004171440</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>18.89999961853027</v>
+        <v>7.389999866485596</v>
       </c>
       <c r="I141" t="n">
-        <v>2.64550269889837</v>
+        <v>2.976995994245176</v>
       </c>
       <c r="J141" t="n">
         <v>-19</v>
@@ -7071,11 +7071,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.06</v>
+        <v>0.61</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7099,30 +7099,30 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>IT0004376858</t>
+          <t>IT0004720733</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>2.220000028610229</v>
+        <v>24.39999961853027</v>
       </c>
       <c r="I142" t="n">
-        <v>2.702702667871647</v>
+        <v>2.500000039085013</v>
       </c>
       <c r="J142" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="K142" t="n">
-        <v>-17</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7131,12 +7131,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7146,30 +7146,30 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>IT0005138703</t>
+          <t>IT0005386369</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>15.53999996185303</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="I143" t="n">
-        <v>3.217503225401416</v>
+        <v>5.319149062089187</v>
       </c>
       <c r="J143" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="K143" t="n">
-        <v>-17</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7193,30 +7193,30 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>IT0005430951</t>
+          <t>IT0001268561</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>3.660000085830688</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="I144" t="n">
-        <v>2.73224037308468</v>
+        <v>6.140351082662987</v>
       </c>
       <c r="J144" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="K144" t="n">
-        <v>-17</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.11</v>
+        <v>0.5105</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7240,44 +7240,44 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>IT0005339160</t>
+          <t>IT0001041000</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>3.170000076293945</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I145" t="n">
-        <v>3.470031462226375</v>
+        <v>5.512958827017695</v>
       </c>
       <c r="J145" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="K145" t="n">
-        <v>-17</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7287,30 +7287,30 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>IT0005545238</t>
+          <t>LU2592315662</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>8.899999618530273</v>
+        <v>7.005000114440918</v>
       </c>
       <c r="I146" t="n">
-        <v>0.9550562207106782</v>
+        <v>3.854389658658117</v>
       </c>
       <c r="J146" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="K146" t="n">
-        <v>-17</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.095</v>
+        <v>0.35</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7334,30 +7334,30 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>IT0005466963</t>
+          <t>IT0003850929</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>4.820000171661377</v>
+        <v>6.965000152587891</v>
       </c>
       <c r="I147" t="n">
-        <v>1.970954286652131</v>
+        <v>5.025125518051213</v>
       </c>
       <c r="J147" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="K147" t="n">
-        <v>-17</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.03</v>
+        <v>1.1</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -7366,12 +7366,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7381,30 +7381,30 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>IT0005521551</t>
+          <t>IT0005203424</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>1.25</v>
+        <v>42</v>
       </c>
       <c r="I148" t="n">
-        <v>2.4</v>
+        <v>2.619047619047619</v>
       </c>
       <c r="J148" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="K148" t="n">
-        <v>-17</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.09</v>
+        <v>0.75</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -7413,45 +7413,45 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>IT0005246142</t>
+          <t>IT0005252736</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>7.949999809265137</v>
+        <v>17.14999961853027</v>
       </c>
       <c r="I149" t="n">
-        <v>1.13207549885865</v>
+        <v>4.373177939838775</v>
       </c>
       <c r="J149" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="K149" t="n">
-        <v>-17</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.1</v>
+        <v>0.43</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -7460,12 +7460,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7475,30 +7475,30 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>IT0005532525</t>
+          <t>IT0003203947</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>8.399999618530273</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="I150" t="n">
-        <v>1.190476244539363</v>
+        <v>3.788546128174832</v>
       </c>
       <c r="J150" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="K150" t="n">
-        <v>-17</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -7507,12 +7507,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7522,30 +7522,30 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>IT0004171440</t>
+          <t>IT0005322612</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>7.389999866485596</v>
+        <v>4.550000190734863</v>
       </c>
       <c r="I151" t="n">
-        <v>2.976995994245176</v>
+        <v>3.296703158506324</v>
       </c>
       <c r="J151" t="n">
-        <v>-19</v>
+        <v>-26</v>
       </c>
       <c r="K151" t="n">
-        <v>-17</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.61</v>
+        <v>0.197169</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -7569,14 +7569,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>IT0004720733</t>
+          <t>IT0005455875</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>24.39999961853027</v>
+        <v>12.23999977111816</v>
       </c>
       <c r="I152" t="n">
-        <v>2.500000039085013</v>
+        <v>1.610857873259486</v>
       </c>
       <c r="J152" t="n">
         <v>-26</v>
@@ -7588,11 +7588,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.15</v>
+        <v>1.1</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -7616,14 +7616,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>IT0005386369</t>
+          <t>IT0005253205</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>2.819999933242798</v>
+        <v>28.45000076293945</v>
       </c>
       <c r="I153" t="n">
-        <v>5.319149062089187</v>
+        <v>3.866432233748553</v>
       </c>
       <c r="J153" t="n">
         <v>-26</v>
@@ -7635,11 +7635,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -7663,14 +7663,14 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>IT0001268561</t>
+          <t>IT0005107492</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>11.39999961853027</v>
+        <v>67.69999694824219</v>
       </c>
       <c r="I154" t="n">
-        <v>6.140351082662987</v>
+        <v>0.6942393222843467</v>
       </c>
       <c r="J154" t="n">
         <v>-26</v>
@@ -7682,11 +7682,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5105</v>
+        <v>1.2</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -7710,14 +7710,14 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0005274094</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>9.260000228881836</v>
+        <v>90.59999847412109</v>
       </c>
       <c r="I155" t="n">
-        <v>5.512958827017695</v>
+        <v>1.324503333565471</v>
       </c>
       <c r="J155" t="n">
         <v>-26</v>
@@ -7729,7 +7729,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7757,14 +7757,14 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>LU2592315662</t>
+          <t>IT0005513202</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>7.005000114440918</v>
+        <v>22.85000038146973</v>
       </c>
       <c r="I156" t="n">
-        <v>3.854389658658117</v>
+        <v>1.181619236290942</v>
       </c>
       <c r="J156" t="n">
         <v>-26</v>
@@ -7776,11 +7776,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -7804,14 +7804,14 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>IT0003850929</t>
+          <t>IT0001018362</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>6.965000152587891</v>
+        <v>10.44999980926514</v>
       </c>
       <c r="I157" t="n">
-        <v>5.025125518051213</v>
+        <v>3.636363702735056</v>
       </c>
       <c r="J157" t="n">
         <v>-26</v>
@@ -7823,11 +7823,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -7851,489 +7851,19 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>IT0005203424</t>
+          <t>IT0005440893</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>42</v>
+        <v>34.29999923706055</v>
       </c>
       <c r="I158" t="n">
-        <v>2.619047619047619</v>
+        <v>0.874635587967755</v>
       </c>
       <c r="J158" t="n">
         <v>-26</v>
       </c>
       <c r="K158" t="n">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>First Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Straordinario</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>IT0005252736</t>
-        </is>
-      </c>
-      <c r="H159" t="n">
-        <v>17.14999961853027</v>
-      </c>
-      <c r="I159" t="n">
-        <v>4.373177939838775</v>
-      </c>
-      <c r="J159" t="n">
-        <v>-26</v>
-      </c>
-      <c r="K159" t="n">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>GEFRAN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>IT0003203947</t>
-        </is>
-      </c>
-      <c r="H160" t="n">
-        <v>11.35000038146973</v>
-      </c>
-      <c r="I160" t="n">
-        <v>3.788546128174832</v>
-      </c>
-      <c r="J160" t="n">
-        <v>-26</v>
-      </c>
-      <c r="K160" t="n">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>IGD SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>IT0005322612</t>
-        </is>
-      </c>
-      <c r="H161" t="n">
-        <v>4.550000190734863</v>
-      </c>
-      <c r="I161" t="n">
-        <v>3.296703158506324</v>
-      </c>
-      <c r="J161" t="n">
-        <v>-26</v>
-      </c>
-      <c r="K161" t="n">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>INTERCOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>0.197169</v>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>IT0005455875</t>
-        </is>
-      </c>
-      <c r="H162" t="n">
-        <v>12.23999977111816</v>
-      </c>
-      <c r="I162" t="n">
-        <v>1.610857873259486</v>
-      </c>
-      <c r="J162" t="n">
-        <v>-26</v>
-      </c>
-      <c r="K162" t="n">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>ITALMOBILIARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>IT0005253205</t>
-        </is>
-      </c>
-      <c r="H163" t="n">
-        <v>28.45000076293945</v>
-      </c>
-      <c r="I163" t="n">
-        <v>3.866432233748553</v>
-      </c>
-      <c r="J163" t="n">
-        <v>-26</v>
-      </c>
-      <c r="K163" t="n">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>IT0005107492</t>
-        </is>
-      </c>
-      <c r="H164" t="n">
-        <v>67.69999694824219</v>
-      </c>
-      <c r="I164" t="n">
-        <v>0.6942393222843467</v>
-      </c>
-      <c r="J164" t="n">
-        <v>-26</v>
-      </c>
-      <c r="K164" t="n">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Pharmanutra S.p.A.</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>IT0005274094</t>
-        </is>
-      </c>
-      <c r="H165" t="n">
-        <v>90.59999847412109</v>
-      </c>
-      <c r="I165" t="n">
-        <v>1.324503333565471</v>
-      </c>
-      <c r="J165" t="n">
-        <v>-26</v>
-      </c>
-      <c r="K165" t="n">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>REVO Insurance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>IT0005513202</t>
-        </is>
-      </c>
-      <c r="H166" t="n">
-        <v>22.85000038146973</v>
-      </c>
-      <c r="I166" t="n">
-        <v>1.181619236290942</v>
-      </c>
-      <c r="J166" t="n">
-        <v>-26</v>
-      </c>
-      <c r="K166" t="n">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>VALSOIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>IT0001018362</t>
-        </is>
-      </c>
-      <c r="H167" t="n">
-        <v>10.44999980926514</v>
-      </c>
-      <c r="I167" t="n">
-        <v>3.636363702735056</v>
-      </c>
-      <c r="J167" t="n">
-        <v>-26</v>
-      </c>
-      <c r="K167" t="n">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>WIIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>IT0005440893</t>
-        </is>
-      </c>
-      <c r="H168" t="n">
-        <v>34.29999923706055</v>
-      </c>
-      <c r="I168" t="n">
-        <v>0.874635587967755</v>
-      </c>
-      <c r="J168" t="n">
-        <v>-26</v>
-      </c>
-      <c r="K168" t="n">
         <v>-24</v>
       </c>
     </row>
@@ -8348,7 +7878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8371,29 +7901,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -8405,29 +7935,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8439,46 +7969,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Homizy SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8490,12 +8020,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8507,12 +8037,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -8524,12 +8054,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -8541,29 +8071,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8575,29 +8105,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8609,63 +8139,63 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Homizy SIIQ S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8677,12 +8207,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -8694,12 +8224,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8711,29 +8241,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -8745,12 +8275,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8762,29 +8292,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8796,12 +8326,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -8813,63 +8343,63 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8881,12 +8411,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -8898,12 +8428,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8915,29 +8445,29 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8949,63 +8479,63 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Giocamondo Study S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -9017,12 +8547,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9034,12 +8564,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9051,46 +8581,46 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -9102,12 +8632,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -9119,12 +8649,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -9136,29 +8666,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -9170,12 +8700,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9187,12 +8717,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9204,12 +8734,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -9221,46 +8751,46 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -9272,12 +8802,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -9289,12 +8819,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -9306,29 +8836,29 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -9340,12 +8870,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9357,12 +8887,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9374,12 +8904,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -9391,12 +8921,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9408,559 +8938,49 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Giocamondo Study S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>CLASS EDITORI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>BEEWIZE</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>DOTSTAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>TALEA GROUP</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Softlab S.p.A.</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>SIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>OSAI Automation System S.p.A.</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Tenax International S.p.A.</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>MEVIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Cube Labs S.p.A.</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>E-NOVIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Cogefeed S.p.A.</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>COFLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>CLASS EDITORI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>BEEWIZE</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Estrima S.p.A.</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Piu' Medical S.p.A.</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>FIDIA S.p.A</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>EXPERT.AI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>ECOSUNTEK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>DBA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Casta Diva Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Cloudia Research S.p.A.</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>BORGOSESIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>ATON Green Storage S.p.A.</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Cyberoo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
         </is>
@@ -9990,248 +9010,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ATON Green Storage S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BORGOSESIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Casta Diva Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cloudia Research S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cyberoo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DBA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ECOSUNTEK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EXPERT.AI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FIDIA S.p.A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Piu' Medical S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>